--- a/CJAP_Robot_Project_Plan_v3.xlsx
+++ b/CJAP_Robot_Project_Plan_v3.xlsx
@@ -2998,7 +2998,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>DOWNGRADED from Done, 26 Sep 2026 - two of five bullets are not met. MET: each topic carries label, definition, phrases, exemplars and matchers (corpus/voice/topic_map.json, 35 topics); full-corpus coverage and orphan census run against the corrected corpus (floor 0.68, 463/9,804 chunk-level orphans, 0/1,104 doc-level). NOT MET: (1) "every document tagged with a primary and secondary topic" - reports/w1_7_pilot_topic_tags.json covers 95 of 1,104 documents; merge_tag_topics.py's tagging step is hard-scoped to pilot_subset_frozen_v4.csv. (2) the independence check is mis-calibrated - at TOPIC_MERGE_COSINE 0.95 it collapsed 34 topics to 3 (220 of 561 pairs above threshold), so it was BYPASSED with CJ_TOPIC_MERGE_COSINE=1.01 and the v4.2 34-topic set restored (sha16 50600bdd34836db7, drift 2.98e-08). Related CE-8 defect: honors_received and robot_identity_meta are byte-identical zero-chunk centroids sharing one gmean fallback, and they are polluting secondary tags. See docs/p3/p3_3_recovery_2026-09-26.md.</t>
+          <t>DOWNGRADED from Done, 26 Sep 2026 - two of five bullets are not met. MET: each topic carries label, definition, phrases, exemplars and matchers (corpus/voice/topic_map.json, 35 topics); full-corpus coverage and orphan census run against the corrected corpus (floor 0.68, 463/9,804 chunk-level orphans, 0/1,104 doc-level). NOT MET: (1) "every document tagged with a primary and secondary topic" - reports/w1_7_pilot_topic_tags.json covers 95 of 1,104 documents; merge_tag_topics.py's tagging step is hard-scoped to pilot_subset_frozen_v4.csv. (2) the independence check is mis-calibrated - at TOPIC_MERGE_COSINE 0.95 it collapsed 34 topics to 3 (220 of 561 pairs above threshold), so it was BYPASSED with CJ_TOPIC_MERGE_COSINE=1.01 and the v4.2 34-topic set restored (sha16 50600bdd34836db7, drift 2.98e-08). Related CE-8 defect: honors_received and robot_identity_meta are byte-identical zero-chunk centroids sharing one gmean fallback, and they are polluting secondary tags. See docs/p3/p3_3_recovery_2026-09-26.md. ALSO MEASURED 26 Sep: zero of 1,104 corpus .json carry topic_paths - apply_topic_paths.py backfills them but generate_corpus_from_xlsx.py rebuilds the .json from the pinned workbooks, which have no topic column, so every regeneration wipes it. The taxonomy itself (layer 1) is a hand-curated dict in build_topic_map.py written against 79 documents and never re-derived; only the assignment and the per-topic stats are derived from enrichment. See the 'Themes &amp; IDs' tab.</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
@@ -13227,8 +13226,8 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C73:D73"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="C54:D54"/>
@@ -13490,7 +13489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13895,9 +13894,167 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>WHERE THE 34 TOPICS COME FROM — three layers, only two of them derived</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>The question</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Are the topics a RESULT of the data enrichment, or something imposed on it? Both, in different layers — and the distinction decides what has to be rebuilt when new material arrives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Layer 1 · the taxonomy
+(NOT derived)</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>WHICH topics exist — the ~35 ids, display names, definitions, default register, wit calibration and matcher keywords — is a HAND-CURATED Python dict inside scripts/build_topic_map.py. Its own docstring says so: 'The taxonomy is a hand-curated dict of ~35 topics with matcher rules.' It was written against 79 documents (64 columns, 15 speeches, NO books) and generated 2026-05-25. It has never been re-derived.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Layer 2 · assignment + stats
+(DERIVED from enrichment)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Each document is scored against every topic by case-insensitive matching against title + primary_topics + sub_topics + Keyword/s + entity names — all enrichment fields. The per-topic statistics are aggregated the same way: doc_count, doc_ids, top_signature_phrases, top_people, top_institutions, top_cases, date_range, type_distribution, theme_distribution. So the enrichment DOES shape the topic map — it just cannot invent a topic the curator never wrote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Layer 3 · centroids
+(DERIVED from embeddings)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>CE-10: centroid = mean(label + description + signature_phrases + exemplar chunks), computed in the 768-d space. This is what retrieval actually scores against. Rebuilding centroids does NOT change which topics exist — that is layer 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>THE GAP</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Layer 1 has never seen the enrichment of the other 1,025 documents, let alone the 186 arriving in batch-04 — 168 of which are BOOK chapters, a format the matchers were never written for. Book chapters are currently assigned by keyword rules designed for newspaper columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>The governed way to fix it</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>The Corpus Expansion runbook already owns this and it is evidence-gated:
+CE-7  tag the new docs against the CURRENT map, then CLUSTER the orphans — do they share a subject?
+CE-8  DECIDE (human, no CC prompt): retag only / expand / full rebuild
+CE-9  if expanding: taxonomy_expansion_PROPOSAL.md, one candidate dimension per section, with a human sign-off
+CE-10 rebuild centroids from scratch under the agreed dimensional model
+Rule 4 of the runbook: add a topic dimension only from evidence you can point at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Never exercised</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>This path has not run. Batch-03 was a CORRECTION (retag only, by design) and batch-04 has not started. CE-7's orphan clustering on 168 book chapters is the first real test of whether the taxonomy fits the corpus it now serves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>A SECOND GAP — the assignment does not persist</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Measured 26 Sep</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>ZERO of 1,104 corpus .json files carry topic_paths or any topic field. Verified across every file: the 21 keys present are id, format, type, theme, theme_label, number, title, date, link, keywords, primary_topics, sub_topics, signature_phrases, entities, stances, notable_anecdotes, target_audience, register_markers, decision_framework_signals, one_paragraph_summary, source_xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>scripts/apply_topic_paths.py backfills topic_paths into the per-doc .json, but generate_corpus_from_xlsx.py rebuilds those .json from the pinned workbooks — which have no topic column — so every regeneration WIPES the backfill. The only live tagging is reports/w1_7_pilot_topic_tags.json, and that covers 95 documents, not 1,104.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>What it means for P3.3</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>'Every document tagged with a primary and secondary topic' fails twice: only 95 are tagged, and even those tags live in a side report rather than in the documents. Fixing it is a choice between adding a topic column to the pinned schema (so it survives regeneration) or treating the tag file as the system of record and regenerating it after every corpus build. That is a CE-8-adjacent decision, not a bug fix.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="11">
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CJAP_Robot_Project_Plan_v3.xlsx
+++ b/CJAP_Robot_Project_Plan_v3.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -186,8 +186,14 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11785,6 +11791,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
@@ -13226,8 +13233,8 @@
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C35:D35"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="C54:D54"/>
@@ -13489,572 +13496,2724 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="96" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>THEMES, IDENTIFIERS AND THE LIVE COUNTS</t>
+          <t>CORPUS INVENTORY, THEMES AND IDENTIFIERS</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Read this as</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>A live inventory, regenerated by scripts/build_project_plan_v3.py from corpus/ and batch-04/intake_manifest.csv. 'Now' is what is pinned and indexed today. '+batch-04' is enriched, QA'd and waiting at CE-4. Re-run the script after any batch and every number here refreshes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>THE CORPUS AT A GLANCE</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>+batch-04</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Columns</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Philippine Daily Inquirer opinion columns, weekly</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>785</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>803</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>2011-04-17 to 2026-05-18. Roughly one a week, unbroken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Book chapters</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>One chapter = one document, across 12 works</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>168</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>299</v>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>4 works represented now; 12 after the merge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Keynotes, inductions, lectures, eulogies</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>153</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>153</v>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>1994-11-23 to 2026-04-27. No new intake in batch-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Biography</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>The authorised life, chapter by chapter</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>1936-01-01 to 2024-01-01. No new intake in batch-04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Active corpus documents</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>1104</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>186</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>Plus 5 retired IDs whose rows stay pinned with no corpus file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>The 1,200-plus figure</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>1104 + 186 = 1290 documents after CE-4. That is the number to hold in mind: the knowledge model is being built for roughly thirteen hundred documents, not the seventy-nine the topic taxonomy was written against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>THE TWELVE BOOKS — chapter counts and where they sit</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Volumes</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Work</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>+batch-04</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Theme spread after the merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A Centenary of Justice</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>A:9 · B:2 · C:3 · D:9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>Battles in the Supreme Court</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>A:6 · B:2 · D:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>Judicial Renaissance</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>A:4 · B:6 · C:1 · D:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Justice and Faith</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>A:1 · B:1 · C:10 · D:2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>Leadership by Example: The Davide Standard</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>A:7 · B:2 · C:1 · D:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>Leveling the Playing Field</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>A:9 · B:4 · D:3 · E:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Liberty and Prosperity</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>A:11 · B:8 · C:3 · D:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Love God, Serve Man</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>A:2 · B:4 · C:14 · D:1 · E:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Reforming the Judiciary</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>A:7 · B:3 · C:2 · D:8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>The Bio-Age Dawns on the Judiciary</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>A:9 · C:2 · D:5 · E:4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Transparency, Unanimity &amp; Diversity</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>A:11 · B:7 · C:3 · D:3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>7 vols</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>With Due Respect</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>A:31 · B:5 · C:5 · D:9 · E:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>18 vols</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>TOTAL — 12 works</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>131</v>
+      </c>
+      <c r="D29" s="21" t="n">
+        <v>168</v>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>299</v>
+      </c>
+      <c r="F29" s="21" t="inlineStr"/>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Works vs volumes</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>With Due Respect is ONE work in SEVEN volumes. Counting works gives 12 — which is the 'all 12 books' target. Counting volumes gives 18. Both are right; say which you mean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>What the merge changes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Books go from 4 works to 12, and from 131 chapters to 299. Eight works enter the corpus for the first time. Every one of those 168 chapters is longer-form than a column — median 2,729 words against roughly 800 — so they chunk differently and carry far more of the doctrinal material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>COLUMNS — the weekly run</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Span</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Cadence</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Theme A</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Other themes</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>2011-04 – 2026-05</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>785</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>514</v>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>B:18 · C:112 · D:24 · E:117</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>Columns are the spine of the corpus and lean heavily to theme A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>53</v>
+      </c>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" s="20" t="inlineStr"/>
+      <c r="D44" s="20" t="inlineStr"/>
+      <c r="E44" s="20" t="inlineStr"/>
+      <c r="F44" s="20" t="inlineStr"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>THE GAP</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>The run begins 17 Apr 2011, but the Inquirer column actually began 11 Feb 2007 — his first, reprinted as BA031 'Visionary Leadership by Example'. Roughly 222 columns from Feb 2007 to Apr 2011 have never been sourced. 803 + ~222 is about 1,025, which is where 'almost a thousand columns' comes from. A batch-05 sourcing job, not a pipeline job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>SPEECHES</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Span</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Documents</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Theme C</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Theme A</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>1994-11-23 – 2026-04-27</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="n">
+        <v>153</v>
+      </c>
+      <c r="C50" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="D50" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>B:21 · D:23 · E:8</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="inlineStr">
+        <is>
+          <t>Thirty-two years of platform speaking — inductions, keynotes, lectures, eulogies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>By decade</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>1990s 3</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>2000s 45</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>2010s 69</t>
+        </is>
+      </c>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>2020s 36</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>BIOGRAPHY — all 35 chapters, in ID order</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Doc ID</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Chapter title</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr"/>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>GC001</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>PROLOGUE: The Republic at Dawn</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>2001-01-20</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E55" s="20" t="inlineStr"/>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>GC002</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>The Boy Who Slept on Pavement</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>1947-01-01</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E56" s="20" t="inlineStr"/>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>GC003</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>FEU and the Construction of Ambition</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>1955-01-01</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E57" s="20" t="inlineStr"/>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>GC004</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>The Bar Exam and the Discipline of Pain</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr"/>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>GC005</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>The Mentor and the Moral Spine</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>1961-01-01</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr"/>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>GC006</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Independence by Design</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>1963-01-01</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E60" s="20" t="inlineStr"/>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>GC007</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>Faith Finds Its Voice</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr"/>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>GC008</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>Rotary, Earthquake, and the Test of Leadership</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr"/>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>GC009</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>LOVE GOD. SERVE MAN.</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>1990-07-01</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr"/>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>GC010</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>The Reckoning of a Year -- and the Quiet Accumulation of Trust</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>1991-06-01</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr"/>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>GC011</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>From Civic Leadership to National Visibility</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E65" s="20" t="inlineStr"/>
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>GC012</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>The Call from Malacañang -- and the First Refusal</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E66" s="20" t="inlineStr"/>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>GC013</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>Seven Rejections</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr"/>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="25" t="inlineStr">
+        <is>
+          <t>GC014</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Ask. Seek. Knock.</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>1995-07-01</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E68" s="20" t="inlineStr"/>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="25" t="inlineStr">
+        <is>
+          <t>GC015</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>The Bench</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>1995-10-01</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E69" s="20" t="inlineStr"/>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>GC016</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>EDSA, Judgment at Dawn</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>2001-01-20</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr"/>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="25" t="inlineStr">
+        <is>
+          <t>GC017</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>Chief Justice</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>2005-12-20</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E71" s="20" t="inlineStr"/>
+      <c r="F71" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="25" t="inlineStr">
+        <is>
+          <t>GC018</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>Retirement Without Retreat</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>2006-12-01</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr"/>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>GC019</t>
+        </is>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>The Elder Statesman</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr"/>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>GC020</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>EPILOGUE: The Judgment That Endures</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>2007-01-01</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr"/>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="25" t="inlineStr">
+        <is>
+          <t>GC021</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 1: Early Years</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>1936-01-01</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr"/>
+      <c r="F75" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
+          <t>GC022</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 2: Return to the City - Boyhood Years</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>1945-01-01</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr"/>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="25" t="inlineStr">
+        <is>
+          <t>GC023</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 3: The Rise of the Student Leader</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr">
+        <is>
+          <t>1955-01-01</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr"/>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="25" t="inlineStr">
+        <is>
+          <t>GC024</t>
+        </is>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 4: The Law Student</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>1956-01-01</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr"/>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="25" t="inlineStr">
+        <is>
+          <t>GC025</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 5: Keeper of Dreams</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>1958-01-01</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr"/>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>GC026</t>
+        </is>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 6: The Lawyer</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>1961-01-01</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E80" s="20" t="inlineStr"/>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="25" t="inlineStr">
+        <is>
+          <t>GC027</t>
+        </is>
+      </c>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 7: Lawyer in the Marketplace</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="inlineStr">
+        <is>
+          <t>1963-01-01</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E81" s="20" t="inlineStr"/>
+      <c r="F81" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="25" t="inlineStr">
+        <is>
+          <t>GC028</t>
+        </is>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 8: Turning Point</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>1986-01-01</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr"/>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>GC029</t>
+        </is>
+      </c>
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 9: Among Bishops, Cardinals and a Pope</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr">
+        <is>
+          <t>1989-01-01</t>
+        </is>
+      </c>
+      <c r="D83" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E83" s="20" t="inlineStr"/>
+      <c r="F83" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="25" t="inlineStr">
+        <is>
+          <t>GC030</t>
+        </is>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 10: Appointment to the Supreme Court</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="inlineStr">
+        <is>
+          <t>1987-01-01</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E84" s="20" t="inlineStr"/>
+      <c r="F84" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>GC031</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 11: Associate Justice</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="inlineStr">
+        <is>
+          <t>1995-01-01</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E85" s="20" t="inlineStr"/>
+      <c r="F85" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="25" t="inlineStr">
+        <is>
+          <t>GC032</t>
+        </is>
+      </c>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 12: Guided by the Word</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>2001-01-01</t>
+        </is>
+      </c>
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E86" s="20" t="inlineStr"/>
+      <c r="F86" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="25" t="inlineStr">
+        <is>
+          <t>GC033</t>
+        </is>
+      </c>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 13: 21st Chief Justice of the Philippines</t>
+        </is>
+      </c>
+      <c r="C87" s="20" t="inlineStr">
+        <is>
+          <t>2005-12-07</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E87" s="20" t="inlineStr"/>
+      <c r="F87" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="25" t="inlineStr">
+        <is>
+          <t>GC034</t>
+        </is>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 14: Liberty and Prosperity (Life after the Supreme Court)</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="inlineStr">
+        <is>
+          <t>2006-12-07</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E88" s="20" t="inlineStr"/>
+      <c r="F88" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="25" t="inlineStr">
+        <is>
+          <t>GC035</t>
+        </is>
+      </c>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>Chapter 15: Papal Award</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr"/>
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>cjp_biography_curated_normalized.xlsx (14 fields — no Link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>All one theme</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Every biography chapter is theme C (biographical and personal) — 35 of 35. That is correct for the material, but it means theme C is carried almost entirely by the biography and by Justice and Faith / Love God, Serve Man.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>THE FIVE THEMES</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>Theme</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Docs now</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t>Folder</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="E94" s="12" t="inlineStr"/>
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>What belongs here</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B95" s="20" t="inlineStr">
         <is>
           <t>Liberty and Rule of Law</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C95" s="20" t="n">
+        <v>606</v>
+      </c>
+      <c r="D95" s="20" t="inlineStr">
         <is>
           <t>A_liberty_rule_of_law</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>Constitutional doctrine, due process, judicial independence and review, civil liberties.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="E95" s="20" t="inlineStr"/>
+      <c r="F95" s="20" t="inlineStr">
+        <is>
+          <t>Constitutional doctrine, due process, judicial independence and review, civil liberties, the courts as the last bulwark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B96" s="20" t="inlineStr">
         <is>
           <t>Prosperity and Economic Philosophy</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C96" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="D96" s="20" t="inlineStr">
         <is>
           <t>B_prosperity_economic_philosophy</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="E96" s="20" t="inlineStr"/>
+      <c r="F96" s="20" t="inlineStr">
         <is>
           <t>Economic governance, business and investment law, MSMEs, social justice as an economic question.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="23" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B97" s="20" t="inlineStr">
         <is>
           <t>Biographical and Personal</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C97" s="20" t="n">
+        <v>225</v>
+      </c>
+      <c r="D97" s="20" t="inlineStr">
         <is>
           <t>C_biographical_personal</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>Early life, family, faith, mentors, friendships, honours.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="E97" s="20" t="inlineStr"/>
+      <c r="F97" s="20" t="inlineStr">
+        <is>
+          <t>Early life, family, faith, mentors, friendships, honours — the man rather than the office.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="23" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B98" s="20" t="inlineStr">
         <is>
           <t>FLP Mission and Foundation</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C98" s="20" t="n">
+        <v>72</v>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
         <is>
           <t>D_flp_mission_foundation</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="E98" s="20" t="inlineStr"/>
+      <c r="F98" s="20" t="inlineStr">
         <is>
           <t>Scholarships, the dissertation contest, donors and partners, the Museum.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="23" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B99" s="20" t="inlineStr">
         <is>
           <t>Current Events Commentary</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C99" s="20" t="n">
+        <v>154</v>
+      </c>
+      <c r="D99" s="20" t="inlineStr">
         <is>
           <t>E_current_events_commentary</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="E99" s="20" t="inlineStr"/>
+      <c r="F99" s="20" t="inlineStr">
         <is>
           <t>Time-bound commentary on Philippine political events, elections, geopolitics.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>FORMAT LETTER, AND THE LIVE COUNT</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>The distribution is lopsided</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Theme A holds 606 of 1104 documents; theme B holds 47. A theme is a SHELF, one per document — not a score, and not the same thing as the 34 retrieval topics. Do not use theme counts to judge retrieval coverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>THE IDENTIFIER</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
         <is>
           <t>Letter</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>Workbook</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="C104" s="12" t="inlineStr">
         <is>
           <t>Documents now</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>After batch-04</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr"/>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>Pinned workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="25" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B105" s="20" t="inlineStr">
         <is>
           <t>column</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C105" s="20" t="n">
+        <v>785</v>
+      </c>
+      <c r="D105" s="20" t="n">
+        <v>803</v>
+      </c>
+      <c r="E105" s="20" t="inlineStr"/>
+      <c r="F105" s="20" t="inlineStr">
         <is>
           <t>cjp_columns_curated_normalized.xlsx</t>
         </is>
       </c>
-      <c r="D12" s="20" t="n">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="25" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B106" s="20" t="inlineStr">
         <is>
           <t>book chapter</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C106" s="20" t="n">
+        <v>131</v>
+      </c>
+      <c r="D106" s="20" t="n">
+        <v>299</v>
+      </c>
+      <c r="E106" s="20" t="inlineStr"/>
+      <c r="F106" s="20" t="inlineStr">
         <is>
           <t>cjp_books_curated_normalized.xlsx</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="25" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B107" s="20" t="inlineStr">
         <is>
           <t>speech</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C107" s="20" t="n">
+        <v>153</v>
+      </c>
+      <c r="D107" s="20" t="n">
+        <v>153</v>
+      </c>
+      <c r="E107" s="20" t="inlineStr"/>
+      <c r="F107" s="20" t="inlineStr">
         <is>
           <t>cjp_speeches_curated_normalized.xlsx</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="25" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B108" s="20" t="inlineStr">
         <is>
           <t>biography chapter</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C108" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="D108" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E108" s="20" t="inlineStr"/>
+      <c r="F108" s="20" t="inlineStr">
         <is>
           <t>cjp_biography_curated_normalized.xlsx (14 fields)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>^[CBSG][A-E]\d{3}$   e.g. CA003 · BA108 · SB028 · GC021. Letter 1 is the format, letter 2 is the theme, digits 3-5 are a position in that format+theme series — a POSITION, not a count. CA529 does not mean there are 529 columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>Never reused</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>An ID is never reused and never renumbered. A retired ID stays retired; a replacement takes a NEW ID and records superseded_doc_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>RETIRED IDENTIFIERS — data/csv/retired_doc_ids.csv</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>Doc ID</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Superseded by</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="25" t="inlineStr">
         <is>
           <t>BA040</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B115" s="20" t="inlineStr">
+        <is>
+          <t>A Centenary of Justice -- Ch. 20: Social Weather Stations v. Comelec -- May Election Surveys Be Banned?</t>
+        </is>
+      </c>
+      <c r="C115" s="20" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="D115" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>A Centenary of Justice -- Ch. 20: Social Weather Stations v. Comelec -- May Election Surveys Be Banned? — No source text (summary-only); chapter text not in data/ and not online</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="E115" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F115" s="20" t="inlineStr">
+        <is>
+          <t>No source text (summary-only); chapter text not in data/ and not online</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="25" t="inlineStr">
         <is>
           <t>BC009</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>A Centenary of Justice -- Appendix D: MPGR (a tribute to Justice Minerva P. Gonzaga-Reyes)</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="D116" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>A Centenary of Justice -- Appendix D: MPGR (a tribute to Justice Minerva P. Gonzaga-Reyes) — No source text (summary-only); not in data/ and not online</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F116" s="20" t="inlineStr">
+        <is>
+          <t>No source text (summary-only); not in data/ and not online</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="25" t="inlineStr">
         <is>
           <t>BC010</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B117" s="20" t="inlineStr">
+        <is>
+          <t>A Centenary of Justice -- Back Matter: Davide Foreword, Accolades &amp; Aquino Book Review</t>
+        </is>
+      </c>
+      <c r="C117" s="20" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="D117" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>A Centenary of Justice -- Back Matter: Davide Foreword, Accolades &amp; Aquino Book Review — No source text (summary-only); paratext written by others about the book</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="E117" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F117" s="20" t="inlineStr">
+        <is>
+          <t>No source text (summary-only); paratext written by others about the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="25" t="inlineStr">
         <is>
           <t>BD018</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>A Centenary of Justice -- Front Matter (Cover, Centennial Prayer, Contents, Foreword, Preface)</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="D118" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>A Centenary of Justice -- Front Matter (Cover, Centennial Prayer, Contents, Foreword, Preface) — No source text (summary-only); not in data/ and not online</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F118" s="20" t="inlineStr">
+        <is>
+          <t>No source text (summary-only); not in data/ and not online</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="28" customHeight="1">
+      <c r="A119" s="25" t="inlineStr">
         <is>
           <t>SA085</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B119" s="20" t="inlineStr">
+        <is>
+          <t>How the Judiciary Can Help the Economy</t>
+        </is>
+      </c>
+      <c r="C119" s="20" t="inlineStr">
         <is>
           <t>speech</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> date 2012-11-29 and link); SB085 carries the full text</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>How the Judiciary Can Help the Economy — Duplicate of SB085 (same title</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>RULE</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>A retired ID is never reused and never renumbered. Its row stays in the pinned sheet; it has no corpus file and no chunks. A replacement takes a NEW ID and records superseded_doc_id — BA108 supersedes the retired BA040.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="D119" s="20" t="inlineStr">
+        <is>
+          <t>SB085</t>
+        </is>
+      </c>
+      <c r="E119" s="20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="F119" s="20" t="inlineStr">
+        <is>
+          <t>Duplicate of SB085 (same title, date 2012-11-29 and link); SB085 carries the full text</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>WHERE THE 34 TOPICS COME FROM — three layers, only two of them derived</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>The question</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>Are the topics a RESULT of the data enrichment, or something imposed on it? Both, in different layers — and the distinction decides what has to be rebuilt when new material arrives.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Layer 1 · the taxonomy
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>Layer 1 · taxonomy
 (NOT derived)</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>WHICH topics exist — the ~35 ids, display names, definitions, default register, wit calibration and matcher keywords — is a HAND-CURATED Python dict inside scripts/build_topic_map.py. Its own docstring says so: 'The taxonomy is a hand-curated dict of ~35 topics with matcher rules.' It was written against 79 documents (64 columns, 15 speeches, NO books) and generated 2026-05-25. It has never been re-derived.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>WHICH topics exist — the ~35 ids, display names, definitions, default register and matcher keywords — is a HAND-CURATED Python dict inside scripts/build_topic_map.py. Its own docstring says so. It was written against 79 documents (64 columns, 15 speeches, NO books), generated 2026-05-25, and never re-derived.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>Layer 2 · assignment + stats
 (DERIVED from enrichment)</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Each document is scored against every topic by case-insensitive matching against title + primary_topics + sub_topics + Keyword/s + entity names — all enrichment fields. The per-topic statistics are aggregated the same way: doc_count, doc_ids, top_signature_phrases, top_people, top_institutions, top_cases, date_range, type_distribution, theme_distribution. So the enrichment DOES shape the topic map — it just cannot invent a topic the curator never wrote.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Each document is scored against every topic by matching title + primary_topics + sub_topics + Keyword/s + entity names. The per-topic statistics — doc_count, doc_ids, top_signature_phrases, top_people, top_institutions, top_cases, date_range, distributions — are aggregated the same way. The enrichment DOES shape the map; it just cannot invent a topic the curator never wrote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>Layer 3 · centroids
 (DERIVED from embeddings)</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>CE-10: centroid = mean(label + description + signature_phrases + exemplar chunks), computed in the 768-d space. This is what retrieval actually scores against. Rebuilding centroids does NOT change which topics exist — that is layer 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>CE-10: centroid = mean(label + description + signature_phrases + exemplar chunks), in the 768-d space. This is what retrieval scores against. Rebuilding centroids does NOT change which topics exist — that is layer 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="14" t="inlineStr">
         <is>
           <t>THE GAP</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Layer 1 has never seen the enrichment of the other 1,025 documents, let alone the 186 arriving in batch-04 — 168 of which are BOOK chapters, a format the matchers were never written for. Book chapters are currently assigned by keyword rules designed for newspaper columns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="72" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>The governed way to fix it</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>The Corpus Expansion runbook already owns this and it is evidence-gated:
-CE-7  tag the new docs against the CURRENT map, then CLUSTER the orphans — do they share a subject?
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>Layer 1 has never seen the enrichment of the other 1,025 documents, let alone the 168 BOOK chapters arriving in batch-04 — a format those keyword matchers were never written for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="69" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>The governed fix</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>CE-7  tag the new docs against the CURRENT map, then CLUSTER the orphans
 CE-8  DECIDE (human, no CC prompt): retag only / expand / full rebuild
-CE-9  if expanding: taxonomy_expansion_PROPOSAL.md, one candidate dimension per section, with a human sign-off
-CE-10 rebuild centroids from scratch under the agreed dimensional model
-Rule 4 of the runbook: add a topic dimension only from evidence you can point at.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Never exercised</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>This path has not run. Batch-03 was a CORRECTION (retag only, by design) and batch-04 has not started. CE-7's orphan clustering on 168 book chapters is the first real test of whether the taxonomy fits the corpus it now serves.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+CE-9  if expanding: taxonomy_expansion_PROPOSAL.md, one candidate dimension per section, with sign-off
+CE-10 rebuild centroids from scratch under the agreed model
+Runbook rule 4: add a topic dimension only from evidence you can point at. Never exercised — batch-03 was a correction (retag only) and batch-04 has not started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>A SECOND GAP — the assignment does not persist</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>Measured 26 Sep</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>ZERO of 1,104 corpus .json files carry topic_paths or any topic field. Verified across every file: the 21 keys present are id, format, type, theme, theme_label, number, title, date, link, keywords, primary_topics, sub_topics, signature_phrases, entities, stances, notable_anecdotes, target_audience, register_markers, decision_framework_signals, one_paragraph_summary, source_xlsx.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="B129" s="4" t="n"/>
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="4" t="n"/>
+      <c r="E129" s="4" t="n"/>
+      <c r="F129" s="4" t="n"/>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="14" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>0 of 1104 corpus .json files carry topic_paths or any topic field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>scripts/apply_topic_paths.py backfills topic_paths into the per-doc .json, but generate_corpus_from_xlsx.py rebuilds those .json from the pinned workbooks — which have no topic column — so every regeneration WIPES the backfill. The only live tagging is reports/w1_7_pilot_topic_tags.json, and that covers 95 documents, not 1,104.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>What it means for P3.3</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>'Every document tagged with a primary and secondary topic' fails twice: only 95 are tagged, and even those tags live in a side report rather than in the documents. Fixing it is a choice between adding a topic column to the pinned schema (so it survives regeneration) or treating the tag file as the system of record and regenerating it after every corpus build. That is a CE-8-adjacent decision, not a bug fix.</t>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>scripts/apply_topic_paths.py backfills topic_paths into the per-doc .json, but generate_corpus_from_xlsx.py rebuilds those .json from the pinned workbooks — which have no topic column — so every regeneration WIPES the backfill. The only live tagging is reports/w1_7_pilot_topic_tags.json, covering 95 documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>What it means</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>P3.3's 'every document tagged with a primary and secondary topic' fails twice: coverage AND persistence. Fixing it is a choice — add a topic column to the pinned schema so it survives regeneration, or treat the tag file as the system of record and regenerate it after every corpus build. A CE-8-adjacent decision, not a bug fix.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
+  <mergeCells count="18">
+    <mergeCell ref="B126:F126"/>
+    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B125:F125"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CJAP_Robot_Project_Plan_v3.xlsx
+++ b/CJAP_Robot_Project_Plan_v3.xlsx
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Topic model — dimensions, not labels</t>
+          <t>Topic model — DERIVE the dimensions, then build them</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>[~] Partial</t>
+          <t>[ ] Not started — reset 26 Sep 2026</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>DOWNGRADED from Done, 26 Sep 2026 - two of five bullets are not met. MET: each topic carries label, definition, phrases, exemplars and matchers (corpus/voice/topic_map.json, 35 topics); full-corpus coverage and orphan census run against the corrected corpus (floor 0.68, 463/9,804 chunk-level orphans, 0/1,104 doc-level). NOT MET: (1) "every document tagged with a primary and secondary topic" - reports/w1_7_pilot_topic_tags.json covers 95 of 1,104 documents; merge_tag_topics.py's tagging step is hard-scoped to pilot_subset_frozen_v4.csv. (2) the independence check is mis-calibrated - at TOPIC_MERGE_COSINE 0.95 it collapsed 34 topics to 3 (220 of 561 pairs above threshold), so it was BYPASSED with CJ_TOPIC_MERGE_COSINE=1.01 and the v4.2 34-topic set restored (sha16 50600bdd34836db7, drift 2.98e-08). Related CE-8 defect: honors_received and robot_identity_meta are byte-identical zero-chunk centroids sharing one gmean fallback, and they are polluting secondary tags. See docs/p3/p3_3_recovery_2026-09-26.md. ALSO MEASURED 26 Sep: zero of 1,104 corpus .json carry topic_paths - apply_topic_paths.py backfills them but generate_corpus_from_xlsx.py rebuilds the .json from the pinned workbooks, which have no topic column, so every regeneration wipes it. The taxonomy itself (layer 1) is a hand-curated dict in build_topic_map.py written against 79 documents and never re-derived; only the assignment and the per-topic stats are derived from enrichment. See the 'Themes &amp; IDs' tab.</t>
+          <t>RESET 26 Sep 2026. This row no longer inherits anything. corpus/voice/topic_map.json records corpus_stats.n_docs = 79 (column 64, speech 15, zero books, zero biography), generated 2026-05-25 and never re-derived, so its 35 topics are PRIOR ART and not a baseline. Three are already degenerate at 79 documents (robot_identity_meta 0, honors_received 2, death_penalty_and_echegaray 1) and the first two are byte-identical zero-chunk centroids sharing one gmean fallback. The taxonomy for the 1,290-document corpus is derived from the corpus at CE-7, decided at CE-8, signed off at CE-9 and built into centroids at CE-10. Separately, zero of 1,104 corpus .json carry topic_paths: the pin was taken before apply_topic_paths.py rather than after it, so every regeneration wiped the backfill. The pipeline order is now generate - chunk - embed - map - centroids - tag - apply - snapshot. See the 'Themes &amp; IDs' tab.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Orphan census — tag the new docs against the CURRENT topic map</t>
+          <t>DERIVE candidate topic dimensions from the corpus — no inherited map</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -7033,7 +7033,7 @@
       <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Tag ONLY the new batch-&lt;id&gt; docs against the EXISTING topic centroids (primary + secondary, up to the config tag cap). Do not create, merge or modify any centroid in this task. Report: (1) the max-cosine distribution for the new docs, (2) every doc below the tagging floor as an orphan list with its best-matching topic and score, (3) a clustering of those orphans — are they scattered, or do they share a subject? — and (4) a re-run of the independence check across existing centroids on the enlarged corpus. Output the tagging table plus the orphan and independence reports.
-FORMATS: source .md -&gt; see tab 'Format · Source .md'. Enriched row (15 fields; biography 14) -&gt; tab 'Format · Enriched row'. Generated corpus files -&gt; tab 'Format · Corpus output'. Themes and IDs -&gt; tab 'Themes &amp; IDs'.</t>
+FORMATS: source .md -&gt; see tab 'Format · Source .md'. Enriched row (15 fields; biography 14) -&gt; tab 'Format · Enriched row'. Generated corpus files -&gt; tab 'Format · Corpus output'. Themes and IDs -&gt; tab 'Themes &amp; IDs'.  DERIVE-FIRST AMENDMENT (26 Sep 2026): the existing topic map is prior art, not the reference. Score the WHOLE corpus against the prior-art matchers for diagnosis only, then derive candidate dimensions from four sources: (1) k-means over the zero-scoring documents, k = 2..40 with a silhouette curve, reported at document and chunk level; (2) every distinct primary_topics / sub_topics value appearing in 15+ documents that no prior-art matcher catches; (3) per-work coverage across all twelve works; (4) pairwise cosine on provisional centroids plus an orphan-rate sweep of the floor from 0.55 to 0.80. Do not assume any prior-art topic survives.</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>DECIDE — retag only, expand, or rebuild  (the branch point)</t>
+          <t>DECIDE — the topic count and the dimension list  (the gate)</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>(human decision — no CC prompt) Read the CE-7 orphan census and independence report, choose one branch, and record it in the decisions register with the evidence attached and a revisit date. Then a one-line CC task notes the chosen branch in the batch folder. Do not start centroid work before the branch is recorded.</t>
+          <t>(human decision — no CC prompt) Read the CE-7 orphan census and independence report, choose one branch, and record it in the decisions register with the evidence attached and a revisit date. Then a one-line CC task notes the chosen branch in the batch folder. Do not start centroid work before the branch is recorded.  DERIVE-FIRST AMENDMENT (26 Sep 2026): the branch is no longer retag / expand / rebuild, because there is nothing to retag against. The decision is the topic count N and the dimension list, taken from the CE-7 evidence, with the tagging floor and the fate of every prior-art topic recorded alongside it.</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Taxonomy expansion proposal + human sign-off  (gate — expansion branch only)</t>
+          <t>Taxonomy proposal + human sign-off  (gate — always, not only on expansion)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>Draft taxonomy_expansion_PROPOSAL.md from the CE-7 orphan clusters: one section per candidate dimension with label, description, signature phrases, at least 3 exemplar chunks, and the evidence for it (orphan cluster size, query-log misses, corpus density). For each candidate, build its provisional centroid and report the cosine against EVERY existing centroid — flag as a duplicate anything above the merge bar and drop it from the proposal. Present for sign-off. Do not modify the live centroids in this task.</t>
+          <t>Draft taxonomy_expansion_PROPOSAL.md from the CE-7 orphan clusters: one section per candidate dimension with label, description, signature phrases, at least 3 exemplar chunks, and the evidence for it (orphan cluster size, query-log misses, corpus density). For each candidate, build its provisional centroid and report the cosine against EVERY existing centroid — flag as a duplicate anything above the merge bar and drop it from the proposal. Present for sign-off. Do not modify the live centroids in this task.  DERIVE-FIRST AMENDMENT (26 Sep 2026): the proposal covers the WHOLE taxonomy, not an increment to an existing one. One section per dimension with label, definition, signature phrases, three or more exemplar doc_ids, and the cluster or vocabulary entry it came from. State the recommended N and why that number and not N plus or minus three. A prior-art topic appears only if the derivation independently produced it.</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>CE-8 (expansion branch)</t>
+          <t>CE-8</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>CE-9 (or CE-8 rebuild branch)</t>
+          <t>CE-9 (sign-off is mandatory)</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -13496,7 +13496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -16058,7 +16058,7 @@
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>WHERE THE 34 TOPICS COME FROM — three layers, only two of them derived</t>
+          <t>THE TOPIC MODEL — nothing is canonical yet</t>
         </is>
       </c>
       <c r="B121" s="4" t="n"/>
@@ -16068,152 +16068,1463 @@
       <c r="F121" s="4" t="n"/>
     </row>
     <row r="122" ht="28" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>The question</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>Are the topics a RESULT of the data enrichment, or something imposed on it? Both, in different layers — and the distinction decides what has to be rebuilt when new material arrives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="28" customHeight="1">
-      <c r="A123" s="7" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>Read this first</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>There is NO canonical topic set for this corpus. The 35 topics in corpus/voice/topic_map.json are PRIOR ART, not a baseline: hand-written against 79 documents and generated 25 May 2026. The taxonomy for the 1,290-document corpus is derived from the corpus itself at CE-7 to CE-9, signed off, and only then built into centroids at CE-10. Nothing carries over because it is already there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>WHY THE 35 CANNOT CARRY OVER</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="4" t="n"/>
+      <c r="D124" s="4" t="n"/>
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>What the evidence says</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr"/>
+      <c r="D125" s="12" t="inlineStr"/>
+      <c r="E125" s="12" t="inlineStr"/>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>Consequence</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="32" customHeight="1">
+      <c r="A126" s="23" t="inlineStr">
+        <is>
+          <t>Built on a sliver</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>corpus_stats records n_docs = 79: column 64 · speech 15. That is 6% of the corpus it now has to cover.</t>
+        </is>
+      </c>
+      <c r="C126" s="20" t="inlineStr"/>
+      <c r="D126" s="20" t="inlineStr"/>
+      <c r="E126" s="20" t="inlineStr"/>
+      <c r="F126" s="20" t="inlineStr">
+        <is>
+          <t>A taxonomy fitted to a sample is not a taxonomy for the population.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="32" customHeight="1">
+      <c r="A127" s="23" t="inlineStr">
+        <is>
+          <t>Never saw a book</t>
+        </is>
+      </c>
+      <c r="B127" s="20" t="inlineStr">
+        <is>
+          <t>Zero book chapters informed it. 299 are arriving — long-form doctrinal argument at a median 2,729 words, against roughly 800 for a column.</t>
+        </is>
+      </c>
+      <c r="C127" s="20" t="inlineStr"/>
+      <c r="D127" s="20" t="inlineStr"/>
+      <c r="E127" s="20" t="inlineStr"/>
+      <c r="F127" s="20" t="inlineStr">
+        <is>
+          <t>The keyword matchers are column-shaped and were never written for this material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="32" customHeight="1">
+      <c r="A128" s="23" t="inlineStr">
+        <is>
+          <t>Never saw the biography</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="inlineStr">
+        <is>
+          <t>Zero biography chapters informed it. 35 are in the corpus.</t>
+        </is>
+      </c>
+      <c r="C128" s="20" t="inlineStr"/>
+      <c r="D128" s="20" t="inlineStr"/>
+      <c r="E128" s="20" t="inlineStr"/>
+      <c r="F128" s="20" t="inlineStr">
+        <is>
+          <t>The one format that is purely narrative has no dimension of its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" s="23" t="inlineStr">
+        <is>
+          <t>Three are already dead</t>
+        </is>
+      </c>
+      <c r="B129" s="20" t="inlineStr">
+        <is>
+          <t>robot_identity_meta holds 0 documents, honors_received 2, death_penalty_and_echegaray 1 — at 79 documents, before the corpus grew.</t>
+        </is>
+      </c>
+      <c r="C129" s="20" t="inlineStr"/>
+      <c r="D129" s="20" t="inlineStr"/>
+      <c r="E129" s="20" t="inlineStr"/>
+      <c r="F129" s="20" t="inlineStr">
+        <is>
+          <t>They would only look thinner at 1,290.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="32" customHeight="1">
+      <c r="A130" s="23" t="inlineStr">
+        <is>
+          <t>Two are the same vector</t>
+        </is>
+      </c>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>honors_received and robot_identity_meta are byte-identical zero-chunk centroids sharing one gmean fallback.</t>
+        </is>
+      </c>
+      <c r="C130" s="20" t="inlineStr"/>
+      <c r="D130" s="20" t="inlineStr"/>
+      <c r="E130" s="20" t="inlineStr"/>
+      <c r="F130" s="20" t="inlineStr">
+        <is>
+          <t>They are polluting secondary tags today. A rebuild must resolve the pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>HOW THE TOPIC COUNT IS DERIVED — four converging lines</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="n"/>
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="n"/>
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>1 · Orphan clustering</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Score every document against the prior-art matchers, take everything that scores zero, and cluster it: k-means over k = 2…40, silhouette curve, the knee. Per cluster — size, format mix, top TF-IDF terms, exemplars. Cross-checked at chunk level, because a 2,729-word chapter averages into mush at document level and may fragment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>2 · Enrichment vocabulary</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Aggregate primary_topics and sub_topics across all 1,290 enriched rows. Every distinct value appearing in 15 or more documents is a candidate dimension. This is the strongest signal available: it is what the curators wrote by hand, document by document, and it was never fed back into the taxonomy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>3 · Per-work coverage</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>For each of the twelve works, which candidate dimensions its chapters land on and how many go unmatched. The eight works entering for the first time carry sustained argument that the columns only glance at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>4 · Separation and viability</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>Provisional centroids for every candidate; pairwise cosine, flagging anything above the merge bar as a rephrase; drop any dimension under the minimum document and chunk counts. The tagging floor is re-derived from the orphan-rate curve swept 0.55 to 0.80, not inherited at 0.68.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>Rule 4</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>A topic dimension is added only from evidence you can point at. Every dimension in the proposal names its cluster or its vocabulary entry, with exemplar doc_ids.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>The gate</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>CE-7 derives · CE-8 DECIDE (human, no CC prompt) · CE-9 proposal + sign-off · CE-10 centroids from scratch. No centroid file is touched before the sign-off is recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>THE 35 PRIOR-ART TOPICS — candidates to test, not a set to preserve</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="n"/>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="n"/>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>Topic id</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>Display name</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Docs @79</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="inlineStr">
+        <is>
+          <t>Standing in the rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="25" t="inlineStr">
+        <is>
+          <t>rule_of_law</t>
+        </is>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>The Rule of Law</t>
+        </is>
+      </c>
+      <c r="C142" s="20" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="D142" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="F142" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="25" t="inlineStr">
+        <is>
+          <t>twin_beacons_doctrine</t>
+        </is>
+      </c>
+      <c r="B143" s="20" t="inlineStr">
+        <is>
+          <t>Liberty and Prosperity — Twin Beacons</t>
+        </is>
+      </c>
+      <c r="C143" s="20" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="D143" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E143" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="F143" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="25" t="inlineStr">
+        <is>
+          <t>foundation_for_liberty_and_prosperity</t>
+        </is>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>Foundation for Liberty and Prosperity (FLP)</t>
+        </is>
+      </c>
+      <c r="C144" s="20" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="D144" s="20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="F144" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="25" t="inlineStr">
+        <is>
+          <t>with_due_respect_persona</t>
+        </is>
+      </c>
+      <c r="B145" s="20" t="inlineStr">
+        <is>
+          <t>'With Due Respect' — the columnist's stance</t>
+        </is>
+      </c>
+      <c r="C145" s="20" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="D145" s="20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E145" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F145" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="25" t="inlineStr">
+        <is>
+          <t>supreme_court_history</t>
+        </is>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>Supreme Court — history and stewardship</t>
+        </is>
+      </c>
+      <c r="C146" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D146" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="n">
+        <v>33</v>
+      </c>
+      <c r="F146" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="25" t="inlineStr">
+        <is>
+          <t>constitutional_doctrine</t>
+        </is>
+      </c>
+      <c r="B147" s="20" t="inlineStr">
+        <is>
+          <t>Constitutional Doctrine (1987 Constitution)</t>
+        </is>
+      </c>
+      <c r="C147" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D147" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E147" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="F147" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="25" t="inlineStr">
+        <is>
+          <t>family_and_marriage</t>
+        </is>
+      </c>
+      <c r="B148" s="20" t="inlineStr">
+        <is>
+          <t>Family — Leni, children, grandchildren</t>
+        </is>
+      </c>
+      <c r="C148" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D148" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E148" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="F148" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="25" t="inlineStr">
+        <is>
+          <t>faith_journey</t>
+        </is>
+      </c>
+      <c r="B149" s="20" t="inlineStr">
+        <is>
+          <t>Faith Journey — BLD, Pontifical Council, Pro Ecclesia</t>
+        </is>
+      </c>
+      <c r="C149" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D149" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E149" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F149" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="25" t="inlineStr">
+        <is>
+          <t>flp_scholarship_programs</t>
+        </is>
+      </c>
+      <c r="B150" s="20" t="inlineStr">
+        <is>
+          <t>FLP Scholarship and Fellowship Programs</t>
+        </is>
+      </c>
+      <c r="C150" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D150" s="20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E150" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F150" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="25" t="inlineStr">
+        <is>
+          <t>mentors_and_legal_lineage</t>
+        </is>
+      </c>
+      <c r="B151" s="20" t="inlineStr">
+        <is>
+          <t>Mentors and Legal Lineage</t>
+        </is>
+      </c>
+      <c r="C151" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D151" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E151" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F151" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="25" t="inlineStr">
+        <is>
+          <t>international_law_disputes</t>
+        </is>
+      </c>
+      <c r="B152" s="20" t="inlineStr">
+        <is>
+          <t>International Law — Arbitral Award, UNCLOS, EEZ</t>
+        </is>
+      </c>
+      <c r="C152" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D152" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E152" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F152" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="25" t="inlineStr">
+        <is>
+          <t>msme_and_entrepreneurship</t>
+        </is>
+      </c>
+      <c r="B153" s="20" t="inlineStr">
+        <is>
+          <t>MSME and Entrepreneurship — the Prosperity Fund</t>
+        </is>
+      </c>
+      <c r="C153" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D153" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E153" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="F153" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="25" t="inlineStr">
+        <is>
+          <t>museum_for_liberty_and_prosperity</t>
+        </is>
+      </c>
+      <c r="B154" s="20" t="inlineStr">
+        <is>
+          <t>Museum for Liberty and Prosperity</t>
+        </is>
+      </c>
+      <c r="C154" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D154" s="20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E154" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F154" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="25" t="inlineStr">
+        <is>
+          <t>due_process</t>
+        </is>
+      </c>
+      <c r="B155" s="20" t="inlineStr">
+        <is>
+          <t>Due Process and Fair Trial</t>
+        </is>
+      </c>
+      <c r="C155" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D155" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E155" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F155" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="25" t="inlineStr">
+        <is>
+          <t>economic_governance_and_business_law</t>
+        </is>
+      </c>
+      <c r="B156" s="20" t="inlineStr">
+        <is>
+          <t>Economic Governance and Business Law</t>
+        </is>
+      </c>
+      <c r="C156" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D156" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E156" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F156" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="25" t="inlineStr">
+        <is>
+          <t>judicial_reform</t>
+        </is>
+      </c>
+      <c r="B157" s="20" t="inlineStr">
+        <is>
+          <t>Judicial Reform — Four Ins and ACID problems</t>
+        </is>
+      </c>
+      <c r="C157" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D157" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E157" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F157" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="25" t="inlineStr">
+        <is>
+          <t>prosperity_fund_msme</t>
+        </is>
+      </c>
+      <c r="B158" s="20" t="inlineStr">
+        <is>
+          <t>Prosperity Fund (MSME)</t>
+        </is>
+      </c>
+      <c r="C158" s="20" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D158" s="20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E158" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F158" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="25" t="inlineStr">
+        <is>
+          <t>robot_identity_meta</t>
+        </is>
+      </c>
+      <c r="B159" s="20" t="inlineStr">
+        <is>
+          <t>Robot Identity (META)</t>
+        </is>
+      </c>
+      <c r="C159" s="20" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D159" s="20" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="E159" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" s="20" t="inlineStr">
+        <is>
+          <t>dead at 79 — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="25" t="inlineStr">
+        <is>
+          <t>bar_exam_and_legal_education</t>
+        </is>
+      </c>
+      <c r="B160" s="20" t="inlineStr">
+        <is>
+          <t>Bar Examination and Legal Education</t>
+        </is>
+      </c>
+      <c r="C160" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D160" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E160" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F160" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="25" t="inlineStr">
+        <is>
+          <t>flp_donors_and_partners</t>
+        </is>
+      </c>
+      <c r="B161" s="20" t="inlineStr">
+        <is>
+          <t>FLP Donors and Institutional Partners</t>
+        </is>
+      </c>
+      <c r="C161" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D161" s="20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E161" s="20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F161" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="25" t="inlineStr">
+        <is>
+          <t>icc_and_duterte</t>
+        </is>
+      </c>
+      <c r="B162" s="20" t="inlineStr">
+        <is>
+          <t>ICC and the Duterte case</t>
+        </is>
+      </c>
+      <c r="C162" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D162" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E162" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F162" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="25" t="inlineStr">
+        <is>
+          <t>philippine_political_landscape</t>
+        </is>
+      </c>
+      <c r="B163" s="20" t="inlineStr">
+        <is>
+          <t>Philippine Political Landscape</t>
+        </is>
+      </c>
+      <c r="C163" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D163" s="20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E163" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F163" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="25" t="inlineStr">
+        <is>
+          <t>eulogies_and_passing</t>
+        </is>
+      </c>
+      <c r="B164" s="20" t="inlineStr">
+        <is>
+          <t>Eulogies and Passing of Loved Ones</t>
+        </is>
+      </c>
+      <c r="C164" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D164" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E164" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F164" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="25" t="inlineStr">
+        <is>
+          <t>early_life_sampaloc</t>
+        </is>
+      </c>
+      <c r="B165" s="20" t="inlineStr">
+        <is>
+          <t>Early Life — Sampaloc, FEU, the Bar</t>
+        </is>
+      </c>
+      <c r="C165" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D165" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E165" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F165" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="25" t="inlineStr">
+        <is>
+          <t>friendships_and_civic_circles</t>
+        </is>
+      </c>
+      <c r="B166" s="20" t="inlineStr">
+        <is>
+          <t>Friendships and Civic Circles</t>
+        </is>
+      </c>
+      <c r="C166" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D166" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E166" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F166" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="25" t="inlineStr">
+        <is>
+          <t>ai_and_technology</t>
+        </is>
+      </c>
+      <c r="B167" s="20" t="inlineStr">
+        <is>
+          <t>AI, Technology, and the Judiciary</t>
+        </is>
+      </c>
+      <c r="C167" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D167" s="20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E167" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="F167" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="A168" s="25" t="inlineStr">
+        <is>
+          <t>global_geopolitics</t>
+        </is>
+      </c>
+      <c r="B168" s="20" t="inlineStr">
+        <is>
+          <t>Global Geopolitics and the ICJ</t>
+        </is>
+      </c>
+      <c r="C168" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D168" s="20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E168" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F168" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="25" t="inlineStr">
+        <is>
+          <t>eez_resource_sovereignty</t>
+        </is>
+      </c>
+      <c r="B169" s="20" t="inlineStr">
+        <is>
+          <t>EEZ Resource Sovereignty</t>
+        </is>
+      </c>
+      <c r="C169" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D169" s="20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E169" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="F169" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="25" t="inlineStr">
+        <is>
+          <t>impeachment_accountability</t>
+        </is>
+      </c>
+      <c r="B170" s="20" t="inlineStr">
+        <is>
+          <t>Impeachment and Accountability</t>
+        </is>
+      </c>
+      <c r="C170" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D170" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E170" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F170" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="25" t="inlineStr">
+        <is>
+          <t>judicial_activism_and_political_question</t>
+        </is>
+      </c>
+      <c r="B171" s="20" t="inlineStr">
+        <is>
+          <t>Judicial Activism and the Political Question Doctrine</t>
+        </is>
+      </c>
+      <c r="C171" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D171" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E171" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F171" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="A172" s="25" t="inlineStr">
+        <is>
+          <t>jbc_discernment_and_appointment</t>
+        </is>
+      </c>
+      <c r="B172" s="20" t="inlineStr">
+        <is>
+          <t>JBC Discernment — the Seven Rejections</t>
+        </is>
+      </c>
+      <c r="C172" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D172" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E172" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F172" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="25" t="inlineStr">
+        <is>
+          <t>asean_law_association</t>
+        </is>
+      </c>
+      <c r="B173" s="20" t="inlineStr">
+        <is>
+          <t>ASEAN Law Association and Regional Order</t>
+        </is>
+      </c>
+      <c r="C173" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D173" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E173" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F173" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="25" t="inlineStr">
+        <is>
+          <t>lawyer_ethics_initiative</t>
+        </is>
+      </c>
+      <c r="B174" s="20" t="inlineStr">
+        <is>
+          <t>Lawyer Ethics Initiative (Super Committee)</t>
+        </is>
+      </c>
+      <c r="C174" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D174" s="20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E174" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F174" s="20" t="inlineStr">
+        <is>
+          <t>candidate — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="25" t="inlineStr">
+        <is>
+          <t>honors_received</t>
+        </is>
+      </c>
+      <c r="B175" s="20" t="inlineStr">
+        <is>
+          <t>Honors Received</t>
+        </is>
+      </c>
+      <c r="C175" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D175" s="20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E175" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F175" s="20" t="inlineStr">
+        <is>
+          <t>dead at 79 — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="A176" s="25" t="inlineStr">
+        <is>
+          <t>death_penalty_and_echegaray</t>
+        </is>
+      </c>
+      <c r="B176" s="20" t="inlineStr">
+        <is>
+          <t>Death Penalty and the Echegaray Reflection</t>
+        </is>
+      </c>
+      <c r="C176" s="20" t="inlineStr">
+        <is>
+          <t>subordinate</t>
+        </is>
+      </c>
+      <c r="D176" s="20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E176" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="20" t="inlineStr">
+        <is>
+          <t>dead at 79 — must re-earn its place</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="28" customHeight="1">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>What 'candidate' means</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>A prior-art topic survives into v2 only if the derivation independently produces it: a cluster, a vocabulary entry with enough documents behind it, or both. Surviving is the normal outcome for the anchors. It is not the default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>THE THREE LAYERS — which are derived, and from what</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="n"/>
+      <c r="C180" s="4" t="n"/>
+      <c r="D180" s="4" t="n"/>
+      <c r="E180" s="4" t="n"/>
+      <c r="F180" s="4" t="n"/>
+    </row>
+    <row r="181" ht="28" customHeight="1">
+      <c r="A181" s="7" t="inlineStr">
         <is>
           <t>Layer 1 · taxonomy
-(NOT derived)</t>
-        </is>
-      </c>
-      <c r="B123" s="8" t="inlineStr">
-        <is>
-          <t>WHICH topics exist — the ~35 ids, display names, definitions, default register and matcher keywords — is a HAND-CURATED Python dict inside scripts/build_topic_map.py. Its own docstring says so. It was written against 79 documents (64 columns, 15 speeches, NO books), generated 2026-05-25, and never re-derived.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>Layer 2 · assignment + stats
-(DERIVED from enrichment)</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>Each document is scored against every topic by matching title + primary_topics + sub_topics + Keyword/s + entity names. The per-topic statistics — doc_count, doc_ids, top_signature_phrases, top_people, top_institutions, top_cases, date_range, distributions — are aggregated the same way. The enrichment DOES shape the map; it just cannot invent a topic the curator never wrote.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
+WHICH topics exist</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>A hand-curated Python list, TAXONOMY, at scripts/build_topic_map.py lines 69-649 — ids, display names, definitions, tier, theme anchor and matcher keywords. This is the layer the rebuild rewrites. Until CE-9 is signed off, it holds prior art and nothing more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="28" customHeight="1">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>Layer 2 · assignment and stats
+DERIVED from enrichment</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>Each document is scored against every topic by matching title + primary_topics + sub_topics + keywords + entity names. doc_count, doc_ids, top_signature_phrases, top_people, top_institutions, top_cases, date_range and the distributions are aggregated the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="28" customHeight="1">
+      <c r="A183" s="5" t="inlineStr">
         <is>
           <t>Layer 3 · centroids
-(DERIVED from embeddings)</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>CE-10: centroid = mean(label + description + signature_phrases + exemplar chunks), in the 768-d space. This is what retrieval scores against. Rebuilding centroids does NOT change which topics exist — that is layer 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="28" customHeight="1">
-      <c r="A126" s="14" t="inlineStr">
-        <is>
-          <t>THE GAP</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>Layer 1 has never seen the enrichment of the other 1,025 documents, let alone the 168 BOOK chapters arriving in batch-04 — a format those keyword matchers were never written for.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="69" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>The governed fix</t>
-        </is>
-      </c>
-      <c r="B127" s="8" t="inlineStr">
-        <is>
-          <t>CE-7  tag the new docs against the CURRENT map, then CLUSTER the orphans
-CE-8  DECIDE (human, no CC prompt): retag only / expand / full rebuild
-CE-9  if expanding: taxonomy_expansion_PROPOSAL.md, one candidate dimension per section, with sign-off
-CE-10 rebuild centroids from scratch under the agreed model
-Runbook rule 4: add a topic dimension only from evidence you can point at. Never exercised — batch-03 was a correction (retag only) and batch-04 has not started.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>A SECOND GAP — the assignment does not persist</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="n"/>
-      <c r="C129" s="4" t="n"/>
-      <c r="D129" s="4" t="n"/>
-      <c r="E129" s="4" t="n"/>
-      <c r="F129" s="4" t="n"/>
-    </row>
-    <row r="130" ht="28" customHeight="1">
-      <c r="A130" s="14" t="inlineStr">
+DERIVED from embeddings</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>CE-10: centroid = mean(label + definition + signature_phrases + exemplar chunks) in the 768-d space. This is what retrieval scores against. Rebuilding centroids does not change which topics exist — that is layer 1, and layer 1 is a decision, not a computation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>PERSISTENCE — the assignment has to survive regeneration</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="n"/>
+      <c r="C185" s="4" t="n"/>
+      <c r="D185" s="4" t="n"/>
+      <c r="E185" s="4" t="n"/>
+      <c r="F185" s="4" t="n"/>
+    </row>
+    <row r="186" ht="28" customHeight="1">
+      <c r="A186" s="14" t="inlineStr">
         <is>
           <t>Measured</t>
         </is>
       </c>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="B186" s="6" t="inlineStr">
         <is>
           <t>0 of 1104 corpus .json files carry topic_paths or any topic field.</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="28" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="187" ht="28" customHeight="1">
+      <c r="A187" s="5" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>scripts/apply_topic_paths.py backfills topic_paths into the per-doc .json, but generate_corpus_from_xlsx.py rebuilds those .json from the pinned workbooks — which have no topic column — so every regeneration WIPES the backfill. The only live tagging is reports/w1_7_pilot_topic_tags.json, covering 95 documents.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="28" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>What it means</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>P3.3's 'every document tagged with a primary and secondary topic' fails twice: coverage AND persistence. Fixing it is a choice — add a topic column to the pinned schema so it survives regeneration, or treat the tag file as the system of record and regenerate it after every corpus build. A CE-8-adjacent decision, not a bug fix.</t>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>apply_topic_paths.py backfills topic_paths into the per-doc .json, but generate_corpus_from_xlsx.py rebuilds those .json from the pinned workbooks, which have no topic column. Every regeneration wiped the backfill, because the pin was taken before the apply step rather than after it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="28" customHeight="1">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>The fixed order</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>generate → chunk → embed → topic map → centroids → tag → apply_topic_paths → snapshot.  The pin is taken LAST, so it includes the tags and verify_pin validates a tagged corpus. Running snapshot before apply is what broke it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B126:F126"/>
-    <mergeCell ref="B130:F130"/>
+  <mergeCells count="23">
+    <mergeCell ref="B138:F138"/>
     <mergeCell ref="B91:F91"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B125:F125"/>
-    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B134:F134"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B136:F136"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B133:F133"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B127:F127"/>
     <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B135:F135"/>
+    <mergeCell ref="B188:F188"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
